--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575276936</v>
+        <v>46157.93119501894</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119501894</v>
+        <v>46157.93185311727</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185311727</v>
+        <v>46157.93406668178</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406668178</v>
+        <v>46157.93724727356</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724727356</v>
+        <v>46158.2822238077</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822238077</v>
+        <v>46158.29708401667</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29708401667</v>
+        <v>46158.29822296606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822296606</v>
+        <v>46158.33393331843</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393331843</v>
+        <v>46158.36863120441</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863120441</v>
+        <v>46158.37294082876</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
